--- a/tamu_data/evals/golden_sets/golden_20260410_v2.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260410_v2.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2466,51 +2466,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>What courses would you recommend taking after CSCE 632 to continue learning about HCl concepts?</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>CSCE 632, Accessible Computing, focuses on universal design principles, ethical and legal motivations for accessible technology, and the development and evaluation of inclusive software solutions for users with disabilities. To explore other courses that complement these concepts or delve into broader Human-Computer Interaction topics, I can assist you in searching the university's course catalog.</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>CSCE 632</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>GRADING</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>54784</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>CSCE 632</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:K43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
